--- a/kemic27/figurer/fig04/saltesoploeselighed.xlsx
+++ b/kemic27/figurer/fig04/saltesoploeselighed.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gentoftehf-my.sharepoint.com/personal/hv_ghf_dk/Documents/GHF2/kemibog/kemic-web-2026/henryvest70.github.io/kemic27/figurer/fig04/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_0F435E7F232A1355C2287F28FE3E5FAE875B2D4E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52F934C1-8368-4106-AB8A-958F08DAC994}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="45" windowWidth="28755" windowHeight="12330"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -16,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="25">
   <si>
     <r>
       <t>NO</t>
@@ -415,14 +421,30 @@
         <scheme val="minor"/>
       </rPr>
       <t>3-</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Al</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3+</t>
     </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -473,7 +495,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -496,220 +518,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -720,68 +533,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kontortema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Kontor">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -819,7 +599,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Kontor">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -853,6 +633,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -887,9 +668,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Kontor">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1062,102 +844,108 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:N11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:O11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="13" width="8" customWidth="1"/>
+    <col min="2" max="14" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="15.75" thickBot="1">
-      <c r="N1" s="1"/>
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="2:14" ht="20.25" customHeight="1" thickBot="1">
-      <c r="B2" s="19"/>
-      <c r="C2" s="20" t="s">
+    <row r="2" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="H2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="I2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="J2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="K2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="L2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="M2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="N2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="22" t="s">
+      <c r="O2" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:14" ht="20.25" customHeight="1">
-      <c r="B3" s="16" t="s">
+    <row r="3" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="N3" s="9" t="s">
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:14" ht="20.25" customHeight="1">
-      <c r="B4" s="17" t="s">
+    <row r="4" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -1187,18 +975,21 @@
       <c r="L4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="10" t="s">
+      <c r="M4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="20.25" customHeight="1">
-      <c r="B5" s="17" t="s">
+    <row r="5" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -1228,18 +1019,21 @@
       <c r="L5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N5" s="10" t="s">
+      <c r="M5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="20.25" customHeight="1">
-      <c r="B6" s="17" t="s">
+    <row r="6" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -1254,33 +1048,36 @@
       <c r="G6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>2</v>
-      </c>
       <c r="L6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N6" s="10" t="s">
+      <c r="M6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="20.25" customHeight="1">
-      <c r="B7" s="17" t="s">
+    <row r="7" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -1304,8 +1101,8 @@
       <c r="J7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>4</v>
+      <c r="K7" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>4</v>
@@ -1313,15 +1110,18 @@
       <c r="M7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N7" s="10" t="s">
+      <c r="N7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:14" ht="20.25" customHeight="1">
-      <c r="B8" s="17" t="s">
+    <row r="8" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -1330,39 +1130,42 @@
       <c r="E8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
+      <c r="F8" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="20.25" customHeight="1">
-      <c r="B9" s="17" t="s">
+    <row r="9" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -1389,21 +1192,24 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N9" s="11" t="s">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="20.25" customHeight="1">
-      <c r="B10" s="17" t="s">
+    <row r="10" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -1412,8 +1218,8 @@
       <c r="E10" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
+      <c r="F10" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>4</v>
@@ -1436,48 +1242,54 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="19.5" thickBot="1">
-      <c r="B11" s="18" t="s">
+    <row r="11" spans="2:15" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="B11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="M11" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="N11" s="15" t="s">
+      <c r="C11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1488,18 +1300,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
